--- a/data/Terre di Pedemonte/investment_decision/Tegna_SFH_from_2015_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Tegna_SFH_from_2015_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>48.06976477779105</v>
+        <v>46.21618539331669</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>7760.08077248697</v>
       </c>
       <c r="F4" t="n">
-        <v>56.68359233574459</v>
+        <v>46.21618539331663</v>
       </c>
       <c r="G4" t="n">
         <v>7760.08077248697</v>
       </c>
       <c r="H4" t="n">
-        <v>48.4446312</v>
+        <v>46.21618539331667</v>
       </c>
       <c r="I4" t="n">
         <v>7760.08077248697</v>
       </c>
       <c r="J4" t="n">
-        <v>55.93389872841762</v>
+        <v>46.21618539331668</v>
       </c>
       <c r="K4" t="n">
         <v>7760.08077248697</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>54.43326914210888</v>
+        <v>51.48383721261325</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>7760.08077248697</v>
       </c>
       <c r="F5" t="n">
-        <v>60.11165648492988</v>
+        <v>51.48899344723529</v>
       </c>
       <c r="G5" t="n">
         <v>7760.08077248697</v>
       </c>
       <c r="H5" t="n">
-        <v>54.43326915334454</v>
+        <v>51.34334575997693</v>
       </c>
       <c r="I5" t="n">
         <v>7760.08077248697</v>
       </c>
       <c r="J5" t="n">
-        <v>60.11165648492988</v>
+        <v>51.17148695835992</v>
       </c>
       <c r="K5" t="n">
         <v>7760.08077248697</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>59.67551345026052</v>
+        <v>51.48383721261325</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>7760.08077248697</v>
       </c>
       <c r="F6" t="n">
-        <v>60.26246455643076</v>
+        <v>51.48899344723529</v>
       </c>
       <c r="G6" t="n">
         <v>7760.08077248697</v>
       </c>
       <c r="H6" t="n">
-        <v>59.67551356172269</v>
+        <v>51.34334575997693</v>
       </c>
       <c r="I6" t="n">
         <v>7760.08077248697</v>
       </c>
       <c r="J6" t="n">
-        <v>60.262464556431</v>
+        <v>51.17148695835992</v>
       </c>
       <c r="K6" t="n">
         <v>7760.08077248697</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>11.64012115873046</v>
+        <v>23.76007415730337</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0034603308</v>
+        <v>0.001424842094117647</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0034603308</v>
+        <v>0.001424842094117647</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0034603308</v>
+        <v>0.001424842094117647</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0034603308</v>
+        <v>0.001424842094117647</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0034603308</v>
+        <v>0.002035488705882353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0034603308</v>
+        <v>0.002035488705882353</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0034603308</v>
+        <v>0.002035488705882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0034603308</v>
+        <v>0.002035488705882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.004681624023529412</v>
+        <v>0.003663879670588235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004681624023529412</v>
+        <v>0.003663879670588235</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.004681624023529412</v>
+        <v>0.003663879670588235</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.004681624023529412</v>
+        <v>0.003663879670588235</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.004802935512539019</v>
+        <v>0.003867428541176471</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004885172894117647</v>
+        <v>0.003867428541176471</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0048029355135304</v>
+        <v>0.003734763540997812</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.004885172894117647</v>
+        <v>0.003867428541176471</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.004885172894117647</v>
+        <v>0.003867428541176471</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.004885172894117648</v>
+        <v>0.003867428541176471</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004885172894117647</v>
+        <v>0.003734763540997812</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0048851728941184</v>
+        <v>0.003867428541176471</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1144,13 +1144,13 @@
         <v>3.63334734</v>
       </c>
       <c r="H19" t="n">
-        <v>1.811518775</v>
+        <v>1.707682271780006</v>
       </c>
       <c r="I19" t="n">
         <v>3.63334734</v>
       </c>
       <c r="J19" t="n">
-        <v>1.811518775</v>
+        <v>1.707682271780006</v>
       </c>
       <c r="K19" t="n">
         <v>3.63334734</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>2.811518775</v>
+        <v>2.004994489539668</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>3.63334734</v>
       </c>
       <c r="F20" t="n">
-        <v>2.811518775</v>
+        <v>2.012406187444417</v>
       </c>
       <c r="G20" t="n">
         <v>3.63334734</v>
       </c>
       <c r="H20" t="n">
-        <v>2.811518775</v>
+        <v>1.750969420249649</v>
       </c>
       <c r="I20" t="n">
         <v>3.63334734</v>
       </c>
       <c r="J20" t="n">
-        <v>2.811518775</v>
+        <v>1.749196915862641</v>
       </c>
       <c r="K20" t="n">
         <v>3.63334734</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>2.811518775</v>
+        <v>2.004994489539668</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>3.63334734</v>
       </c>
       <c r="F21" t="n">
-        <v>2.811518775</v>
+        <v>2.012406187444417</v>
       </c>
       <c r="G21" t="n">
         <v>3.63334734</v>
       </c>
       <c r="H21" t="n">
-        <v>2.811518775</v>
+        <v>1.750969420249649</v>
       </c>
       <c r="I21" t="n">
         <v>3.63334734</v>
       </c>
       <c r="J21" t="n">
-        <v>2.811518775</v>
+        <v>1.749196915862641</v>
       </c>
       <c r="K21" t="n">
         <v>3.63334734</v>
@@ -1514,13 +1514,13 @@
         <v>3.63334734</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1038365032199938</v>
       </c>
       <c r="I29" t="n">
         <v>3.63334734</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1038365032199938</v>
       </c>
       <c r="K29" t="n">
         <v>3.63334734</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.8065242854603325</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>3.63334734</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.7991125875555829</v>
       </c>
       <c r="G30" t="n">
         <v>3.63334734</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.060549354750351</v>
       </c>
       <c r="I30" t="n">
         <v>3.63334734</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.062321859137359</v>
       </c>
       <c r="K30" t="n">
         <v>3.63334734</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.8065242854603325</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>3.63334734</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.7991125875555829</v>
       </c>
       <c r="G31" t="n">
         <v>3.63334734</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.060549354750351</v>
       </c>
       <c r="I31" t="n">
         <v>3.63334734</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.062321859137359</v>
       </c>
       <c r="K31" t="n">
         <v>3.63334734</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.822114304218469</v>
+        <v>1.850391906678066</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>14.01734125710063</v>
       </c>
       <c r="F54" t="n">
-        <v>1.822114304218469</v>
+        <v>1.709165822419988</v>
       </c>
       <c r="G54" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="H54" t="n">
-        <v>1.732864188825458</v>
+        <v>1.845777280221772</v>
       </c>
       <c r="I54" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="J54" t="n">
-        <v>1.738705933598122</v>
+        <v>1.709165822419987</v>
       </c>
       <c r="K54" t="n">
         <v>14.01734125710063</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.593228892579639</v>
+        <v>2.540659212058829</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>14.01734125710063</v>
       </c>
       <c r="F55" t="n">
-        <v>2.593228892579639</v>
+        <v>2.290512760951059</v>
       </c>
       <c r="G55" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="H55" t="n">
-        <v>2.385708824145353</v>
+        <v>2.513915646306827</v>
       </c>
       <c r="I55" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="J55" t="n">
-        <v>2.385556685315203</v>
+        <v>2.290512760951059</v>
       </c>
       <c r="K55" t="n">
         <v>14.01734125710063</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.593228892579639</v>
+        <v>2.540659212058829</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>14.01734125710063</v>
       </c>
       <c r="F56" t="n">
-        <v>2.593228892579639</v>
+        <v>2.290512760951059</v>
       </c>
       <c r="G56" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="H56" t="n">
-        <v>2.385708824145353</v>
+        <v>2.513915646306827</v>
       </c>
       <c r="I56" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="J56" t="n">
-        <v>2.385556685315203</v>
+        <v>2.290512760951059</v>
       </c>
       <c r="K56" t="n">
         <v>14.01734125710063</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>3.500736852061893</v>
+        <v>1.642052887933775</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>14.01734125710063</v>
       </c>
       <c r="F64" t="n">
-        <v>3.310725950048211</v>
+        <v>1.783278972191853</v>
       </c>
       <c r="G64" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="H64" t="n">
-        <v>3.581717855200294</v>
+        <v>1.64666751439007</v>
       </c>
       <c r="I64" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="J64" t="n">
-        <v>3.410671679653713</v>
+        <v>1.783278972191854</v>
       </c>
       <c r="K64" t="n">
         <v>14.01734125710063</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>3.589250843899594</v>
+        <v>1.811819979244732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>14.01734125710063</v>
       </c>
       <c r="F65" t="n">
-        <v>3.463992299572661</v>
+        <v>2.061844403713516</v>
       </c>
       <c r="G65" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="H65" t="n">
-        <v>3.796770912086035</v>
+        <v>1.85186174319407</v>
       </c>
       <c r="I65" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="J65" t="n">
-        <v>3.671664506837097</v>
+        <v>2.06935846242754</v>
       </c>
       <c r="K65" t="n">
         <v>14.01734125710063</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>3.992706269079079</v>
+        <v>1.811819979244732</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>14.01734125710063</v>
       </c>
       <c r="F66" t="n">
-        <v>3.979758818207676</v>
+        <v>2.061844403713516</v>
       </c>
       <c r="G66" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="H66" t="n">
-        <v>4.20022633505464</v>
+        <v>1.85186174319407</v>
       </c>
       <c r="I66" t="n">
         <v>14.01734125710063</v>
       </c>
       <c r="J66" t="n">
-        <v>4.187431025472107</v>
+        <v>2.06935846242754</v>
       </c>
       <c r="K66" t="n">
         <v>14.01734125710063</v>
